--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20232.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20232.xlsx
@@ -82,7 +82,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ESCOBAR</t>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
   </si>
   <si>
     <t>BASILIO</t>
@@ -97,10 +100,10 @@
     <t>RAMOS</t>
   </si>
   <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>APALE</t>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
   </si>
   <si>
     <t>SANCHEZ</t>
@@ -115,10 +118,10 @@
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
+    <t>GIANCARLO</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
   </si>
   <si>
     <t>CLARA LIZBETH</t>
@@ -131,9 +134,6 @@
   </si>
   <si>
     <t>SAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
   </si>
 </sst>
 </file>
@@ -677,16 +677,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -700,16 +703,19 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H3">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -723,16 +729,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>70.97</v>
+      </c>
+      <c r="H4">
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -746,16 +755,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -811,16 +823,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -860,16 +872,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>74.19</v>
+        <v>70.97</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -895,7 +907,7 @@
         <v>80.65000000000001</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -937,7 +949,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920237</v>
+        <v>23330051920300</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -949,10 +961,10 @@
         <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -960,7 +972,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920287</v>
+        <v>22330051920235</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -972,18 +984,18 @@
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920288</v>
+        <v>23330051920287</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1006,7 +1018,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920302</v>
+        <v>23330051920288</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1029,7 +1041,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920304</v>
+        <v>23330051920302</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1052,7 +1064,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920256</v>
+        <v>23330051920304</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1064,10 +1076,10 @@
         <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>1</v>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20232.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="60">
   <si>
     <t>Mat</t>
   </si>
@@ -82,52 +82,115 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
     <t>VILLEGAS</t>
   </si>
   <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>CLARA LIZBETH</t>
+  </si>
+  <si>
+    <t>HEIDI KESEI</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>JULIO ALBERTO</t>
+  </si>
+  <si>
     <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
   </si>
   <si>
     <t>ANA ISABEL</t>
@@ -832,7 +895,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -907,7 +970,7 @@
         <v>80.65000000000001</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -949,22 +1012,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920300</v>
+        <v>23330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -972,22 +1035,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920235</v>
+        <v>23330051920303</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -995,85 +1058,85 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920287</v>
+        <v>22330051920231</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920288</v>
+        <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920302</v>
+        <v>22330051920235</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920304</v>
+        <v>23330051920319</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1082,6 +1145,167 @@
         <v>13</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920287</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920288</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920289</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920290</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920300</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920302</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920304</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20232.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -82,121 +82,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
+  </si>
+  <si>
     <t>CUAPIO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
     <t>TINOCO</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
   </si>
   <si>
     <t>JESSICA</t>
   </si>
   <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
-  </si>
-  <si>
     <t>CRISTIAN</t>
   </si>
   <si>
     <t>JULIO ALBERTO</t>
-  </si>
-  <si>
-    <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>ANA ISABEL</t>
-  </si>
-  <si>
-    <t>SAUL</t>
   </si>
 </sst>
 </file>
@@ -909,16 +855,19 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -980,7 +929,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1012,22 +961,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920222</v>
+        <v>23330051920303</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1035,22 +984,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920303</v>
+        <v>22330051920231</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1058,19 +1007,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920231</v>
+        <v>22330051920233</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -1081,19 +1030,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920233</v>
+        <v>22330051920235</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -1104,39 +1053,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920235</v>
+        <v>23330051920222</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920319</v>
+        <v>23330051920289</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1150,16 +1099,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920287</v>
+        <v>23330051920290</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1168,144 +1117,6 @@
         <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920288</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920289</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920290</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920300</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920302</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920304</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20232.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -82,61 +82,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
     <t>DE ROMAN</t>
   </si>
   <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
     <t>TINOCO</t>
   </si>
   <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
     <t>NATHALI</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
   </si>
   <si>
     <t>CRISTIAN</t>
@@ -832,16 +796,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>93.09999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -858,16 +822,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>58.33</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -884,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>70.97</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -910,16 +874,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>80.65000000000001</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -961,22 +925,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920303</v>
+        <v>22330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -984,139 +948,47 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920231</v>
+        <v>23330051920289</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920233</v>
+        <v>23330051920290</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920235</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920222</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920289</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920290</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>
